--- a/DateBase/orders/Dang Nguyen48_2026-8-1.xlsx
+++ b/DateBase/orders/Dang Nguyen48_2026-8-1.xlsx
@@ -774,6 +774,9 @@
       <c r="C41" t="str">
         <v>281_莱拉_undefined_Rosa rugosa Thunb._10stems</v>
       </c>
+      <c r="F41" t="str">
+        <v>5</v>
+      </c>
     </row>
   </sheetData>
   <ignoredErrors>
@@ -832,7 +835,7 @@
         <v>0.00</v>
       </c>
       <c r="G2" t="str">
-        <v>084205510101055114451010510101055555555555555510520200</v>
+        <v>084205510101055114451010510101055555555555555510520205</v>
       </c>
     </row>
   </sheetData>

--- a/DateBase/orders/Dang Nguyen48_2026-8-1.xlsx
+++ b/DateBase/orders/Dang Nguyen48_2026-8-1.xlsx
@@ -398,7 +398,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:L41"/>
+  <dimension ref="A1:L87"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -778,9 +778,401 @@
         <v>5</v>
       </c>
     </row>
+    <row r="42">
+      <c r="A42" t="str">
+        <v>6</v>
+      </c>
+      <c r="C42" t="str">
+        <v>801_烟花菊橙红_undefined_undefined_1bunch</v>
+      </c>
+      <c r="F42" t="str">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="43">
+      <c r="C43" t="str">
+        <v>802_烟花菊粉_undefined_undefined_1bunch</v>
+      </c>
+      <c r="F43" t="str">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="44">
+      <c r="C44" t="str">
+        <v>803_烟花菊粉紫_undefined_undefined_1bunch</v>
+      </c>
+      <c r="F44" t="str">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="45">
+      <c r="C45" t="str">
+        <v>592_进口春兰叶_undefined_undefined_1bunch</v>
+      </c>
+      <c r="F45" t="str">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="46">
+      <c r="C46" t="str">
+        <v>860_大菊白_undefined_undefined_1bunch</v>
+      </c>
+      <c r="F46" t="str">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="47">
+      <c r="C47" t="str">
+        <v>798_大菊粉_undefined_undefined_5stems</v>
+      </c>
+      <c r="F47" t="str">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="48">
+      <c r="C48" t="str">
+        <v>797_大菊黄_undefined_undefined_5stems</v>
+      </c>
+      <c r="F48" t="str">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="49">
+      <c r="C49" t="str">
+        <v>447_黄金球_craspedia_undefined_1bunch</v>
+      </c>
+      <c r="F49" t="str">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="str">
+        <v>7</v>
+      </c>
+      <c r="C50" t="str">
+        <v>576_迷你菊紫_undefined_undefined_1bunch</v>
+      </c>
+      <c r="F50" t="str">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="51">
+      <c r="C51" t="str">
+        <v>789_迷你菊浅粉_undefined_undefined_1bunch</v>
+      </c>
+      <c r="F51" t="str">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="52">
+      <c r="C52" t="str">
+        <v>574_迷你菊白_undefined_undefined_1bunch</v>
+      </c>
+      <c r="F52" t="str">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="53">
+      <c r="C53" t="str">
+        <v>563_星芹_Astrantia_undefined_1bunch</v>
+      </c>
+      <c r="F53" t="str">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="54">
+      <c r="C54" t="str">
+        <v>563_星芹_Astrantia_undefined_1bunch</v>
+      </c>
+      <c r="F54" t="str">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" t="str">
+        <v>8</v>
+      </c>
+      <c r="C55" t="str">
+        <v>470_海芋白_Calla Lily_undefined_1bunch</v>
+      </c>
+      <c r="F55" t="str">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" t="str">
+        <v>1</v>
+      </c>
+      <c r="C56" t="str">
+        <v>341_南天竹绿_undefined_Nandina domestica Thunb._1bunch</v>
+      </c>
+      <c r="F56" t="str">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="57">
+      <c r="C57" t="str">
+        <v>431_小米果_undefined_undefined_1bunch</v>
+      </c>
+      <c r="F57" t="str">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="58">
+      <c r="C58" t="str">
+        <v>521_商陆_phytolacca acinosa _undefined_1bunch</v>
+      </c>
+      <c r="F58" t="str">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="59">
+      <c r="C59" t="str">
+        <v>328_卢荀草_undefined_undefined_1bunch</v>
+      </c>
+      <c r="F59" t="str">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="60">
+      <c r="C60" t="str">
+        <v>431_小米果_undefined_undefined_1bunch</v>
+      </c>
+      <c r="F60" t="str">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="61">
+      <c r="C61" t="str">
+        <v>484_天鹅绒_Star of Bethlehem_undefined_1bunch</v>
+      </c>
+      <c r="F61" t="str">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="62">
+      <c r="C62" t="str">
+        <v>792_珍珠梅白_undefined_undefined_1bunch</v>
+      </c>
+      <c r="F62" t="str">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="63">
+      <c r="C63" t="str">
+        <v>741_袋鼠爪红_undefined_undefined_1bunch</v>
+      </c>
+      <c r="F63" t="str">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="64">
+      <c r="C64" t="str">
+        <v>854_彼岸花黄_undefined_undefined_1bunch</v>
+      </c>
+      <c r="F64" t="str">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="65">
+      <c r="C65" t="str">
+        <v>789_迷你菊浅粉_undefined_undefined_1bunch</v>
+      </c>
+      <c r="F65" t="str">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="66">
+      <c r="C66" t="str">
+        <v>789_迷你菊浅粉_undefined_undefined_1bunch</v>
+      </c>
+      <c r="F66" t="str">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="67">
+      <c r="C67" t="str">
+        <v>789_迷你菊浅粉_undefined_undefined_1bunch</v>
+      </c>
+      <c r="F67" t="str">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="68">
+      <c r="C68" t="str">
+        <v>625_多丁紫蝴蝶_undefined_undefined_1bunch</v>
+      </c>
+      <c r="F68" t="str">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="69">
+      <c r="C69" t="str">
+        <v>600_康乃馨复古红_vintage red_undefined_20stems</v>
+      </c>
+      <c r="F69" t="str">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="70">
+      <c r="C70" t="str">
+        <v>603_康乃馨粉钻_darkpink_undefined_20stems</v>
+      </c>
+      <c r="F70" t="str">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="71">
+      <c r="C71" t="str">
+        <v>604_康乃馨粉佳人_pink_undefined_20stems</v>
+      </c>
+      <c r="F71" t="str">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" t="str">
+        <v>3</v>
+      </c>
+      <c r="C72" t="str">
+        <v>193_粉爱神_Pink Cupid_Rosa rugosa Thunb._20stems</v>
+      </c>
+      <c r="F72" t="str">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="73">
+      <c r="C73" t="str">
+        <v>157_流沙_Quicksand_Rosa rugosa Thunb._20stems</v>
+      </c>
+      <c r="F73" t="str">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="74">
+      <c r="C74" t="str">
+        <v>175_火灵鸟_Free Spirit_Rosa rugosa Thunb._20stems</v>
+      </c>
+      <c r="F74" t="str">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="75">
+      <c r="C75" t="str">
+        <v>283_窒息_undefined_Rosa rugosa Thunb._20stems</v>
+      </c>
+      <c r="F75" t="str">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="76">
+      <c r="C76" t="str">
+        <v>177_国王日_Kings Day_Rosa rugosa Thunb._20stems</v>
+      </c>
+      <c r="F76" t="str">
+        <v>5.5</v>
+      </c>
+    </row>
+    <row r="77">
+      <c r="C77" t="str">
+        <v>137_凯瑟琳_Catherine_Rosa rugosa Thunb._20stems</v>
+      </c>
+      <c r="F77" t="str">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="78">
+      <c r="C78" t="str">
+        <v>170_奶油杯_Butter Cup_Rosa rugosa Thunb._20stems</v>
+      </c>
+      <c r="F78" t="str">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="79">
+      <c r="C79" t="str">
+        <v>47_拉丝玫红_Spider Dark Pink_Gerbera L._20stems</v>
+      </c>
+      <c r="F79" t="str">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="80">
+      <c r="C80" t="str">
+        <v>72_泽娜_undefined_Gerbera L._20stems</v>
+      </c>
+      <c r="F80" t="str">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="81">
+      <c r="C81" t="str">
+        <v>70_朝霞mini_undefined_Gerbera L._20stems</v>
+      </c>
+      <c r="F81" t="str">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="82">
+      <c r="C82" t="str">
+        <v>87_紫霞非洲菊_undefined_Gerbera L._10stems</v>
+      </c>
+      <c r="F82" t="str">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="83">
+      <c r="C83" t="str">
+        <v>87_紫霞非洲菊_undefined_Gerbera L._10stems</v>
+      </c>
+      <c r="F83" t="str">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" t="str">
+        <v>4</v>
+      </c>
+      <c r="C84" t="str">
+        <v>845_干花紫罗兰_undefined_undefined_1bunch</v>
+      </c>
+      <c r="F84" t="str">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" t="str">
+        <v>5</v>
+      </c>
+      <c r="C85" t="str">
+        <v>177_国王日_Kings Day_Rosa rugosa Thunb._20stems</v>
+      </c>
+      <c r="F85" t="str">
+        <v>6.5</v>
+      </c>
+    </row>
+    <row r="86">
+      <c r="C86" t="str">
+        <v>181_月光女神_undefined_Rosa rugosa Thunb._20stems</v>
+      </c>
+      <c r="F86" t="str">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" t="str">
+        <v>7</v>
+      </c>
+      <c r="C87" t="str">
+        <v>470_海芋白_Calla Lily_undefined_1bunch</v>
+      </c>
+      <c r="F87" t="str">
+        <v>10</v>
+      </c>
+    </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:L41"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:L87"/>
   </ignoredErrors>
 </worksheet>
 </file>
@@ -835,7 +1227,7 @@
         <v>0.00</v>
       </c>
       <c r="G2" t="str">
-        <v>084205510101055114451010510101055555555555555510520205</v>
+        <v>084205510101055114451010510101055555555555555510520205555155551055555101010101010105555551015151559845.55510101066256.5610</v>
       </c>
     </row>
   </sheetData>

--- a/DateBase/orders/Dang Nguyen48_2026-8-1.xlsx
+++ b/DateBase/orders/Dang Nguyen48_2026-8-1.xlsx
@@ -1229,6 +1229,9 @@
       <c r="G2" t="str">
         <v>084205510101055114451010510101055555555555555510520205555155551055555101010101010105555551015151559845.55510101066256.5610</v>
       </c>
+      <c r="H2" t="str">
+        <v>CNY</v>
+      </c>
     </row>
   </sheetData>
   <ignoredErrors>
